--- a/scenario1/XLSX Files/Scenario_1/Scenario_1_NOVS.xlsx
+++ b/scenario1/XLSX Files/Scenario_1/Scenario_1_NOVS.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J26"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1205,7 +1205,7 @@
         <v>0</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F23" t="n">
         <v>0</v>
@@ -1294,34 +1294,306 @@
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
+          <t>Griewank-20</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>1</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="1" t="inlineStr">
+        <is>
+          <t>Griewank-100</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>1</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0</v>
+      </c>
+      <c r="F27" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="1" t="inlineStr">
+        <is>
+          <t>Griewank-200</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" t="n">
+        <v>0</v>
+      </c>
+      <c r="F28" t="n">
+        <v>0</v>
+      </c>
+      <c r="G28" t="n">
+        <v>0</v>
+      </c>
+      <c r="H28" t="n">
+        <v>1</v>
+      </c>
+      <c r="I28" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="1" t="inlineStr">
+        <is>
+          <t>Griewank-500</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>0</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0</v>
+      </c>
+      <c r="E29" t="n">
+        <v>0</v>
+      </c>
+      <c r="F29" t="n">
+        <v>0</v>
+      </c>
+      <c r="G29" t="n">
+        <v>0</v>
+      </c>
+      <c r="H29" t="n">
+        <v>1</v>
+      </c>
+      <c r="I29" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="1" t="inlineStr">
+        <is>
+          <t>Rosenbrock-20</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>1</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0</v>
+      </c>
+      <c r="E30" t="n">
+        <v>0</v>
+      </c>
+      <c r="F30" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="1" t="inlineStr">
+        <is>
+          <t>Rosenbrock-100</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>1</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" t="n">
+        <v>0</v>
+      </c>
+      <c r="G31" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" t="n">
+        <v>0</v>
+      </c>
+      <c r="J31" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="1" t="inlineStr">
+        <is>
+          <t>Rosenbrock-200</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>1</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" t="n">
+        <v>0</v>
+      </c>
+      <c r="F32" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" t="n">
+        <v>1</v>
+      </c>
+      <c r="I32" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="1" t="inlineStr">
+        <is>
+          <t>Rosenbrock-500</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0</v>
+      </c>
+      <c r="E33" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" t="n">
+        <v>1</v>
+      </c>
+      <c r="I33" t="n">
+        <v>0</v>
+      </c>
+      <c r="J33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="1" t="inlineStr">
+        <is>
           <t>NOVS</t>
         </is>
       </c>
-      <c r="B26" t="n">
-        <v>18</v>
-      </c>
-      <c r="C26" t="n">
-        <v>0</v>
-      </c>
-      <c r="D26" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>0</v>
-      </c>
-      <c r="H26" t="n">
-        <v>6</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0</v>
-      </c>
-      <c r="J26" t="n">
+      <c r="B34" t="n">
+        <v>23</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" t="n">
+        <v>3</v>
+      </c>
+      <c r="F34" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" t="n">
+        <v>0</v>
+      </c>
+      <c r="H34" t="n">
+        <v>10</v>
+      </c>
+      <c r="I34" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" t="n">
         <v>0</v>
       </c>
     </row>
